--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-11.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.36</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -660,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.39</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -691,6 +699,256 @@
         <v>41.67</v>
       </c>
       <c r="T3" t="n">
+        <v>39.79</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Scottish Premiership</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Motherwell x Celtic</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1815</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>40</v>
+      </c>
+      <c r="T4" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Swiss Super League</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Grasshoppers Zurich x Young Boys</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Grasshoppers Zurich</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1968</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T5" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Republic of North Macedonian Soccer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FK Skopje x Vardar Skopje</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FK Skopje</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vardar Skopje</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>200</v>
+      </c>
+      <c r="S6" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="T6" t="n">
         <v>39.79</v>
       </c>
     </row>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-11.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,15 +836,19 @@
       <c r="K5" t="n">
         <v>1.49</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -918,15 +922,19 @@
       <c r="K6" t="n">
         <v>1.37</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -950,6 +958,420 @@
       </c>
       <c r="T6" t="n">
         <v>39.79</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Union St Gilloise x Oud-Heverlee Leuven</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Union St Gilloise</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Oud-Heverlee Leuven</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>478</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>200</v>
+      </c>
+      <c r="S7" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="T7" t="n">
+        <v>35.37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Hacken x Orgryte</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hacken</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orgryte</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>200</v>
+      </c>
+      <c r="S8" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="T8" t="n">
+        <v>32.93</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Csikszereda x Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Csikszereda</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S9" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="T9" t="n">
+        <v>35.37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Lyn x Stromsgodset</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stromsgodset</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S10" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="T10" t="n">
+        <v>41.52</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf x Haugesund</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>365</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>200</v>
+      </c>
+      <c r="S11" t="n">
+        <v>48.78</v>
+      </c>
+      <c r="T11" t="n">
+        <v>46.58</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-11.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-11.xlsx
@@ -1094,15 +1094,19 @@
       <c r="K8" t="n">
         <v>1.31</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1176,15 +1180,19 @@
       <c r="K9" t="n">
         <v>1.27</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1258,15 +1266,19 @@
       <c r="K10" t="n">
         <v>1.6</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1340,15 +1352,19 @@
       <c r="K11" t="n">
         <v>1.65</v>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-11.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,6 +1388,260 @@
       </c>
       <c r="T11" t="n">
         <v>46.58</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Italian Serie A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cagliari x Juventus</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>8530</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>200</v>
+      </c>
+      <c r="S12" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="T12" t="n">
+        <v>28.09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Patronato x CA Guemes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Patronato</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CA Guemes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>200</v>
+      </c>
+      <c r="S13" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="T13" t="n">
+        <v>45.48</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Central Espanol x Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>200</v>
+      </c>
+      <c r="S14" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="T14" t="n">
+        <v>32.93</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-11.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,26 +509,6 @@
           <t>Liquidez_Lay</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Hora_Str</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risco_Red_R$</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Stake_Sugerida_R$</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Lucro_Green_R$</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -601,20 +581,6 @@
       <c r="P2" t="n">
         <v>308</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>200</v>
-      </c>
-      <c r="S2" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="T2" t="n">
-        <v>35.37</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,20 +653,6 @@
       <c r="P3" t="n">
         <v>429</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>200</v>
-      </c>
-      <c r="S3" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="T3" t="n">
-        <v>39.79</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -773,20 +725,6 @@
       <c r="P4" t="n">
         <v>1815</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>200</v>
-      </c>
-      <c r="S4" t="n">
-        <v>40</v>
-      </c>
-      <c r="T4" t="n">
-        <v>38.2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -859,20 +797,6 @@
       <c r="P5" t="n">
         <v>1968</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>200</v>
-      </c>
-      <c r="S5" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="T5" t="n">
-        <v>34.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -945,20 +869,6 @@
       <c r="P6" t="n">
         <v>108</v>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>200</v>
-      </c>
-      <c r="S6" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="T6" t="n">
-        <v>39.79</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1031,20 +941,6 @@
       <c r="P7" t="n">
         <v>478</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>200</v>
-      </c>
-      <c r="S7" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="T7" t="n">
-        <v>35.37</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1117,20 +1013,6 @@
       <c r="P8" t="n">
         <v>160</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>200</v>
-      </c>
-      <c r="S8" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="T8" t="n">
-        <v>32.93</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1203,20 +1085,6 @@
       <c r="P9" t="n">
         <v>289</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S9" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="T9" t="n">
-        <v>35.37</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1289,20 +1157,6 @@
       <c r="P10" t="n">
         <v>187</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S10" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="T10" t="n">
-        <v>41.52</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1375,20 +1229,6 @@
       <c r="P11" t="n">
         <v>365</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>200</v>
-      </c>
-      <c r="S11" t="n">
-        <v>48.78</v>
-      </c>
-      <c r="T11" t="n">
-        <v>46.58</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1461,20 +1301,6 @@
       <c r="P12" t="n">
         <v>8530</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>200</v>
-      </c>
-      <c r="S12" t="n">
-        <v>29.41</v>
-      </c>
-      <c r="T12" t="n">
-        <v>28.09</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1547,20 +1373,6 @@
       <c r="P13" t="n">
         <v>142</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="R13" t="n">
-        <v>200</v>
-      </c>
-      <c r="S13" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="T13" t="n">
-        <v>45.48</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1610,15 +1422,19 @@
       <c r="K14" t="n">
         <v>1.65</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1628,20 +1444,6 @@
       </c>
       <c r="P14" t="n">
         <v>79</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>200</v>
-      </c>
-      <c r="S14" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="T14" t="n">
-        <v>32.93</v>
       </c>
     </row>
   </sheetData>
